--- a/TP4/tabla_diff_medias_train_vs_test_2025.xlsx
+++ b/TP4/tabla_diff_medias_train_vs_test_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,23 +473,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ad_equiv_hogar</t>
+          <t>Distincion_vivienda_hogar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.87838779956427</v>
+        <v>1.021241830065359</v>
       </c>
       <c r="C2" t="n">
-        <v>2.855209656925032</v>
+        <v>1.010165184243965</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0231781426392379</v>
+        <v>0.01107664582139489</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4558758459975484</v>
+        <v>2.227614353220493</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6485457339093281</v>
+        <v>0.02600996523658239</v>
       </c>
       <c r="G2" t="n">
         <v>1836</v>
@@ -501,28 +501,560 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>medio_busqueda_empleo</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.01525054466230937</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.005082592121982211</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.01016795254032716</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.539144917978151</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1238896425285048</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H3" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>busqueda_empleo</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.05010893246187364</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.03557814485387548</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.01453078760799816</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.524605778116728</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1275380709245599</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H4" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>horastrab</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>16.24727668845316</v>
+      </c>
+      <c r="C5" t="n">
+        <v>15.2566709021601</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9906057862930577</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.128806014781267</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2591578718626003</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H5" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adulto_equiv</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.8187037037037036</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8128335451080051</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.005870158595698505</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9406025628650139</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3470592607021338</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H6" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>parentesco</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.869281045751634</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.795425667090216</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.073855378661418</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8305831540840183</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4063394779099996</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H7" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>categoria_inactividad</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.44880174291939</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.512071156289708</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.06326941337031777</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.8171195834519295</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4139907194337183</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H8" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>estado_empleo</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.081154684095861</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.119440914866582</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.03828623077072146</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.7792096669961792</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.435981897596751</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H9" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>n_personas</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.547930283224401</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.508259212198221</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.03967107102617984</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.6526782399033056</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5140630034616107</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H10" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>educ</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>11.54901960784314</v>
+      </c>
+      <c r="C11" t="n">
+        <v>11.44472681067344</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.104292797169693</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.4592124788847587</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6461498902056443</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H11" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ad_equiv_hogar</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.87838779956427</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.855209656925032</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0231781426392379</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4558758459975484</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.6485457339093281</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H12" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tipo_empleo</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3.351307189542484</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.382465057179161</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.03115786763667749</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.4389071516814466</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6607920347323522</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H13" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>nivel_ocupacion</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4.840958605664488</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4.803049555273189</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0379090503912991</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.4220394566414434</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6730579911208867</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H14" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tipo_contrato</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.720043572984749</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.697585768742058</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.02245780424269106</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.4107525750874182</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.6813127092143657</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H15" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>genero</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.521786492374728</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.529860228716645</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.008073736341917659</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.3793737057433555</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.7044645102966782</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H16" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tipo_cobertura_salud</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.628540305010893</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.636594663278272</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.008054358267378658</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.3577048166937333</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.7206158836826305</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H17" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>empleo</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.6236383442265795</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6149936467598475</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.008644697466732021</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.2901695982135241</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.7717269530910418</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H18" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>edad</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B19" t="n">
         <v>36.9281045751634</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C19" t="n">
         <v>36.72935196950445</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D19" t="n">
         <v>0.1987526056589459</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E19" t="n">
         <v>0.2114102560357396</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F19" t="n">
         <v>0.8325966422375486</v>
       </c>
-      <c r="G3" t="n">
-        <v>1836</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="G19" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H19" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>obra_social</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.4869281045751634</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.48284625158831</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.004081852986853374</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1343656731925033</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.8931315316348636</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H20" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>nivel_educ</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4.314814814814815</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4.306226175349428</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.008588639465386905</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1157198511501463</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9078904567514227</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H21" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>edad2</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1836.912854030501</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1841.041931385006</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-4.129077354505171</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.05297137173972552</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9577619587689159</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1836</v>
+      </c>
+      <c r="H22" t="n">
         <v>787</v>
       </c>
     </row>
